--- a/resources/table/class.xlsx
+++ b/resources/table/class.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ability" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="promotion" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ability" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="promotion" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -662,16 +662,16 @@
         <v>0</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>300</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -679,10 +679,10 @@
         <v>2</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>0</v>
@@ -691,10 +691,10 @@
         <v>300</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -708,16 +708,16 @@
         <v>0</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="7" t="n">
         <v>300</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
@@ -725,10 +725,10 @@
         <v>4</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
@@ -737,10 +737,10 @@
         <v>300</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -754,16 +754,16 @@
         <v>0</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -785,22 +785,22 @@
         <v>5</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="7" t="n">
         <v>1200</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -814,16 +814,16 @@
         <v>0</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>1200</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -834,19 +834,19 @@
         <v>0</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="7" t="n">
         <v>1200</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -854,22 +854,22 @@
         <v>8</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="7" t="n">
         <v>1200</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -880,19 +880,19 @@
         <v>0</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="7" t="n">
         <v>2400</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -906,16 +906,16 @@
         <v>0</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="7" t="n">
         <v>2400</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -923,22 +923,22 @@
         <v>11</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="7" t="n">
         <v>2400</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -952,16 +952,16 @@
         <v>0</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="7" t="n">
         <v>4800</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
@@ -972,19 +972,19 @@
         <v>0</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="7" t="n">
         <v>4800</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -992,22 +992,22 @@
         <v>14</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="7" t="n">
         <v>4800</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -1018,19 +1018,19 @@
         <v>0</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="7" t="n">
         <v>4800</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -1044,16 +1044,16 @@
         <v>0</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>9600</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -1061,22 +1061,22 @@
         <v>17</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="7" t="n">
         <v>9600</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -1090,16 +1090,16 @@
         <v>0</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="7" t="n">
         <v>19200</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
@@ -1110,19 +1110,19 @@
         <v>0</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="7" t="n">
         <v>19200</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -1130,22 +1130,22 @@
         <v>20</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="7" t="n">
         <v>19200</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
@@ -1156,19 +1156,19 @@
         <v>0</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="7" t="n">
         <v>38400</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
@@ -1182,16 +1182,16 @@
         <v>0</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="7" t="n">
         <v>38400</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
@@ -1199,22 +1199,22 @@
         <v>23</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="7" t="n">
         <v>38400</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
@@ -1228,16 +1228,16 @@
         <v>0</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="7" t="n">
         <v>38400</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
@@ -1248,19 +1248,19 @@
         <v>0</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="7" t="n">
         <v>76800</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
@@ -1268,22 +1268,22 @@
         <v>26</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="7" t="n">
         <v>76800</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33">
@@ -1294,19 +1294,19 @@
         <v>0</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="7" t="n">
         <v>76800</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34">
@@ -1320,16 +1320,16 @@
         <v>0</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="7" t="n">
         <v>153600</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H34" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35">
@@ -1337,22 +1337,22 @@
         <v>29</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="7" t="n">
         <v>142600</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36">
@@ -1366,16 +1366,16 @@
         <v>0</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="7" t="n">
         <v>153600</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H36" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
@@ -1386,19 +1386,19 @@
         <v>0</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="7" t="n">
         <v>225000</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38">
@@ -1406,22 +1406,22 @@
         <v>32</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="7" t="n">
         <v>225000</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39">
@@ -1432,19 +1432,19 @@
         <v>0</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="7" t="n">
         <v>225000</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40">
@@ -1458,16 +1458,16 @@
         <v>0</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="7" t="n">
         <v>312600</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H40" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41">
@@ -1475,22 +1475,22 @@
         <v>35</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" s="7" t="n">
         <v>384000</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42">
@@ -1504,16 +1504,16 @@
         <v>0</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" s="7" t="n">
         <v>225000</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H42" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43">
@@ -1524,19 +1524,19 @@
         <v>0</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" s="7" t="n">
         <v>450000</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44">
@@ -1544,22 +1544,22 @@
         <v>38</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" s="7" t="n">
         <v>450000</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H44" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45">
@@ -1570,19 +1570,19 @@
         <v>0</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" s="7" t="n">
         <v>450000</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46">
@@ -1596,16 +1596,16 @@
         <v>0</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" s="7" t="n">
         <v>491520</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H46" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47">
@@ -1613,22 +1613,22 @@
         <v>41</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="7" t="n">
         <v>491520</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48">
@@ -1642,16 +1642,16 @@
         <v>0</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" s="7" t="n">
         <v>491520</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H48" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49">
@@ -1662,19 +1662,19 @@
         <v>0</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" s="7" t="n">
         <v>720000</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50">
@@ -1682,22 +1682,22 @@
         <v>44</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="7" t="n">
         <v>720000</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H50" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
@@ -1708,19 +1708,19 @@
         <v>0</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" s="7" t="n">
         <v>983040</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52">
@@ -1734,16 +1734,16 @@
         <v>0</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="7" t="n">
         <v>983040</v>
       </c>
       <c r="G52" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H52" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53">
@@ -1751,22 +1751,22 @@
         <v>47</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" s="7" t="n">
         <v>983040</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54">
@@ -1780,16 +1780,16 @@
         <v>0</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" s="7" t="n">
         <v>1440000</v>
       </c>
       <c r="G54" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H54" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55">
@@ -1800,19 +1800,19 @@
         <v>0</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" s="7" t="n">
         <v>1440000</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56">
@@ -1820,22 +1820,22 @@
         <v>50</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" s="7" t="n">
         <v>1440000</v>
       </c>
       <c r="G56" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H56" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57">
@@ -1846,19 +1846,19 @@
         <v>0</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" s="7" t="n">
         <v>1630000</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58">
@@ -1872,16 +1872,16 @@
         <v>0</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" s="7" t="n">
         <v>1630000</v>
       </c>
       <c r="G58" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H58" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59">
@@ -1889,22 +1889,22 @@
         <v>53</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" s="7" t="n">
         <v>1630000</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60">
@@ -1918,16 +1918,16 @@
         <v>0</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" s="7" t="n">
         <v>2400000</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H60" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61">
@@ -1938,19 +1938,19 @@
         <v>0</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" s="7" t="n">
         <v>2400000</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62">
@@ -1958,22 +1958,22 @@
         <v>56</v>
       </c>
       <c r="C62" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" s="7" t="n">
         <v>2400000</v>
       </c>
       <c r="G62" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H62" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63">
@@ -1984,19 +1984,19 @@
         <v>0</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="7" t="n">
         <v>3500000</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64">
@@ -2010,16 +2010,16 @@
         <v>0</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" s="7" t="n">
         <v>5500000</v>
       </c>
       <c r="G64" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H64" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65">
@@ -2027,22 +2027,22 @@
         <v>59</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" s="7" t="n">
         <v>4500000</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66">
@@ -2056,16 +2056,16 @@
         <v>0</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" s="7" t="n">
         <v>7400000</v>
       </c>
       <c r="G66" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H66" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67">
@@ -2076,19 +2076,19 @@
         <v>0</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" s="7" t="n">
         <v>7400000</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68">
@@ -2096,22 +2096,22 @@
         <v>62</v>
       </c>
       <c r="C68" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" s="7" t="n">
         <v>8400000</v>
       </c>
       <c r="G68" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H68" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69">
@@ -2122,19 +2122,19 @@
         <v>0</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" s="7" t="n">
         <v>9320000</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70">
@@ -2148,16 +2148,16 @@
         <v>0</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" s="7" t="n">
         <v>8320000</v>
       </c>
       <c r="G70" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H70" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="71">
@@ -2165,22 +2165,22 @@
         <v>65</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" s="7" t="n">
         <v>9320000</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72">
@@ -2194,16 +2194,16 @@
         <v>0</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" s="7" t="n">
         <v>10450000</v>
       </c>
       <c r="G72" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H72" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="73">
@@ -2214,19 +2214,19 @@
         <v>0</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" s="7" t="n">
         <v>11000000</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74">
@@ -2234,22 +2234,22 @@
         <v>68</v>
       </c>
       <c r="C74" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" s="7" t="n">
         <v>13000000</v>
       </c>
       <c r="G74" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H74" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="75">
@@ -2260,19 +2260,19 @@
         <v>0</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" s="7" t="n">
         <v>15000000</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76">
@@ -2286,16 +2286,16 @@
         <v>0</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" s="7" t="n">
         <v>17000000</v>
       </c>
       <c r="G76" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H76" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77">
@@ -2303,22 +2303,22 @@
         <v>71</v>
       </c>
       <c r="C77" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" s="7" t="n">
         <v>20000000</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78">
@@ -2332,16 +2332,16 @@
         <v>0</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" s="7" t="n">
         <v>23000000</v>
       </c>
       <c r="G78" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H78" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79">
@@ -2352,19 +2352,19 @@
         <v>0</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" s="7" t="n">
         <v>25000000</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80">
@@ -2372,22 +2372,22 @@
         <v>74</v>
       </c>
       <c r="C80" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" s="7" t="n">
         <v>30000000</v>
       </c>
       <c r="G80" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H80" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="81">
@@ -2398,19 +2398,19 @@
         <v>0</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" s="7" t="n">
         <v>35000000</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82">
@@ -2424,16 +2424,16 @@
         <v>0</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" s="7" t="n">
         <v>40000000</v>
       </c>
       <c r="G82" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H82" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83">
@@ -2441,22 +2441,22 @@
         <v>77</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" s="7" t="n">
         <v>45000000</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="84">
@@ -2470,16 +2470,16 @@
         <v>0</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" s="7" t="n">
         <v>50000000</v>
       </c>
       <c r="G84" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H84" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="85">
@@ -2490,19 +2490,19 @@
         <v>0</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" s="7" t="n">
         <v>50000000</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="86">
@@ -2510,22 +2510,22 @@
         <v>80</v>
       </c>
       <c r="C86" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" s="7" t="n">
         <v>55000000</v>
       </c>
       <c r="G86" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H86" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="87">
@@ -2536,19 +2536,19 @@
         <v>0</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" s="7" t="n">
         <v>60000000</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88">
@@ -2562,16 +2562,16 @@
         <v>0</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" s="7" t="n">
         <v>65000000</v>
       </c>
       <c r="G88" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H88" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89">
@@ -2579,22 +2579,22 @@
         <v>83</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89" s="7" t="n">
         <v>70000000</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="90">
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90" s="7" t="n">
         <v>80000000</v>
       </c>
       <c r="G90" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H90" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="91">
@@ -2628,19 +2628,19 @@
         <v>0</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" s="7" t="n">
         <v>95000000</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H91" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="92">
@@ -2648,22 +2648,22 @@
         <v>86</v>
       </c>
       <c r="C92" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" s="7" t="n">
         <v>95000000</v>
       </c>
       <c r="G92" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H92" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="93">
@@ -2674,19 +2674,19 @@
         <v>0</v>
       </c>
       <c r="D93" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" s="7" t="n">
         <v>105000000</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94">
@@ -2700,16 +2700,16 @@
         <v>0</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" s="7" t="n">
         <v>105000000</v>
       </c>
       <c r="G94" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H94" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="95">
@@ -2717,22 +2717,22 @@
         <v>89</v>
       </c>
       <c r="C95" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D95" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E95" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" s="7" t="n">
         <v>145000000</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H95" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="96">
@@ -2746,16 +2746,16 @@
         <v>0</v>
       </c>
       <c r="E96" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" s="7" t="n">
         <v>130000000</v>
       </c>
       <c r="G96" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H96" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="97">
@@ -2766,19 +2766,19 @@
         <v>0</v>
       </c>
       <c r="D97" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E97" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" s="7" t="n">
         <v>100000000</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H97" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="98">
@@ -2786,22 +2786,22 @@
         <v>92</v>
       </c>
       <c r="C98" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E98" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" s="7" t="n">
         <v>100000000</v>
       </c>
       <c r="G98" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H98" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="99">
@@ -2812,19 +2812,19 @@
         <v>0</v>
       </c>
       <c r="D99" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E99" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" s="7" t="n">
         <v>110000000</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H99" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="100">
@@ -2838,16 +2838,16 @@
         <v>0</v>
       </c>
       <c r="E100" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100" s="7" t="n">
         <v>120000000</v>
       </c>
       <c r="G100" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H100" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="101">
@@ -2855,22 +2855,22 @@
         <v>95</v>
       </c>
       <c r="C101" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D101" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E101" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" s="7" t="n">
         <v>130000000</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H101" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="102">
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="E102" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F102" s="7" t="n">
         <v>120000000</v>
       </c>
       <c r="G102" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H102" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="103">
@@ -2904,19 +2904,19 @@
         <v>0</v>
       </c>
       <c r="D103" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E103" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F103" s="7" t="n">
         <v>220000000</v>
       </c>
       <c r="G103" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H103" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="104">
@@ -2924,22 +2924,22 @@
         <v>98</v>
       </c>
       <c r="C104" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E104" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104" s="7" t="n">
         <v>230000000</v>
       </c>
       <c r="G104" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H104" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="105">
@@ -2950,19 +2950,19 @@
         <v>0</v>
       </c>
       <c r="D105" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E105" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F105" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G105" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H105" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="106">
@@ -2984,22 +2984,22 @@
         <v>5</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D107" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F107" s="7" t="n">
         <v>960</v>
       </c>
       <c r="G107" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H107" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="108">
@@ -3008,7 +3008,7 @@
         <v>6</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D108" s="1" t="n">
         <v>0</v>
@@ -3020,10 +3020,10 @@
         <v>1080</v>
       </c>
       <c r="G108" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H108" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="109">
@@ -3032,10 +3032,10 @@
         <v>7</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D109" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E109" s="1" t="n">
         <v>0</v>
@@ -3044,10 +3044,10 @@
         <v>1080</v>
       </c>
       <c r="G109" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H109" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="110">
@@ -3056,22 +3056,22 @@
         <v>8</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D110" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F110" s="7" t="n">
         <v>1080</v>
       </c>
       <c r="G110" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H110" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="111">
@@ -3080,10 +3080,10 @@
         <v>9</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D111" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E111" s="1" t="n">
         <v>0</v>
@@ -3092,10 +3092,10 @@
         <v>2160</v>
       </c>
       <c r="G111" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H111" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="112">
@@ -3104,7 +3104,7 @@
         <v>10</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D112" s="1" t="n">
         <v>0</v>
@@ -3116,10 +3116,10 @@
         <v>2160</v>
       </c>
       <c r="G112" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H112" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="113">
@@ -3128,22 +3128,22 @@
         <v>11</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D113" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F113" s="7" t="n">
         <v>2160</v>
       </c>
       <c r="G113" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H113" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="114">
@@ -3152,7 +3152,7 @@
         <v>12</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D114" s="1" t="n">
         <v>0</v>
@@ -3164,10 +3164,10 @@
         <v>4320</v>
       </c>
       <c r="G114" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H114" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="115">
@@ -3176,10 +3176,10 @@
         <v>13</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D115" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E115" s="1" t="n">
         <v>0</v>
@@ -3188,10 +3188,10 @@
         <v>4320</v>
       </c>
       <c r="G115" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H115" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="116">
@@ -3200,22 +3200,22 @@
         <v>14</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D116" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116" s="7" t="n">
         <v>4320</v>
       </c>
       <c r="G116" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H116" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="117">
@@ -3224,10 +3224,10 @@
         <v>15</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D117" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E117" s="1" t="n">
         <v>0</v>
@@ -3236,10 +3236,10 @@
         <v>8640</v>
       </c>
       <c r="G117" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H117" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="118">
@@ -3248,7 +3248,7 @@
         <v>16</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D118" s="1" t="n">
         <v>0</v>
@@ -3260,10 +3260,10 @@
         <v>8640</v>
       </c>
       <c r="G118" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H118" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="119">
@@ -3272,22 +3272,22 @@
         <v>17</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D119" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F119" s="7" t="n">
         <v>8640</v>
       </c>
       <c r="G119" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H119" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="120">
@@ -3296,7 +3296,7 @@
         <v>18</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D120" s="1" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>17280</v>
       </c>
       <c r="G120" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H120" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="121">
@@ -3320,10 +3320,10 @@
         <v>19</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D121" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E121" s="1" t="n">
         <v>0</v>
@@ -3332,10 +3332,10 @@
         <v>17280</v>
       </c>
       <c r="G121" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H121" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="122">
@@ -3344,22 +3344,22 @@
         <v>20</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D122" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F122" s="7" t="n">
         <v>17280</v>
       </c>
       <c r="G122" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H122" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="123">
@@ -3368,10 +3368,10 @@
         <v>21</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D123" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E123" s="1" t="n">
         <v>0</v>
@@ -3380,10 +3380,10 @@
         <v>34560</v>
       </c>
       <c r="G123" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H123" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="124">
@@ -3392,7 +3392,7 @@
         <v>22</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D124" s="1" t="n">
         <v>0</v>
@@ -3404,10 +3404,10 @@
         <v>34560</v>
       </c>
       <c r="G124" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H124" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="125">
@@ -3416,22 +3416,22 @@
         <v>23</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D125" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F125" s="7" t="n">
         <v>34560</v>
       </c>
       <c r="G125" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H125" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="126">
@@ -3440,7 +3440,7 @@
         <v>24</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D126" s="1" t="n">
         <v>0</v>
@@ -3452,10 +3452,10 @@
         <v>69120</v>
       </c>
       <c r="G126" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H126" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="127">
@@ -3464,10 +3464,10 @@
         <v>25</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D127" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E127" s="1" t="n">
         <v>0</v>
@@ -3476,10 +3476,10 @@
         <v>69120</v>
       </c>
       <c r="G127" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H127" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="128">
@@ -3488,22 +3488,22 @@
         <v>26</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D128" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F128" s="7" t="n">
         <v>69120</v>
       </c>
       <c r="G128" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H128" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="129">
@@ -3512,10 +3512,10 @@
         <v>27</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D129" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E129" s="1" t="n">
         <v>0</v>
@@ -3524,10 +3524,10 @@
         <v>138240</v>
       </c>
       <c r="G129" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H129" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="130">
@@ -3536,7 +3536,7 @@
         <v>28</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D130" s="1" t="n">
         <v>0</v>
@@ -3548,10 +3548,10 @@
         <v>138240</v>
       </c>
       <c r="G130" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H130" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="131">
@@ -3560,22 +3560,22 @@
         <v>29</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D131" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F131" s="7" t="n">
         <v>138240</v>
       </c>
       <c r="G131" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H131" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="132">
@@ -3584,7 +3584,7 @@
         <v>30</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D132" s="1" t="n">
         <v>0</v>
@@ -3596,10 +3596,10 @@
         <v>200000</v>
       </c>
       <c r="G132" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H132" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="133">
@@ -3608,10 +3608,10 @@
         <v>31</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D133" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E133" s="1" t="n">
         <v>0</v>
@@ -3620,10 +3620,10 @@
         <v>200000</v>
       </c>
       <c r="G133" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H133" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="134">
@@ -3632,22 +3632,22 @@
         <v>32</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D134" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F134" s="7" t="n">
         <v>200000</v>
       </c>
       <c r="G134" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H134" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="135">
@@ -3656,10 +3656,10 @@
         <v>33</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D135" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E135" s="1" t="n">
         <v>0</v>
@@ -3668,10 +3668,10 @@
         <v>270000</v>
       </c>
       <c r="G135" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H135" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="136">
@@ -3680,7 +3680,7 @@
         <v>34</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D136" s="1" t="n">
         <v>0</v>
@@ -3692,10 +3692,10 @@
         <v>270000</v>
       </c>
       <c r="G136" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H136" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="137">
@@ -3704,22 +3704,22 @@
         <v>35</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D137" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F137" s="7" t="n">
         <v>270000</v>
       </c>
       <c r="G137" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H137" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="138">
@@ -3728,7 +3728,7 @@
         <v>36</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D138" s="1" t="n">
         <v>0</v>
@@ -3740,10 +3740,10 @@
         <v>410000</v>
       </c>
       <c r="G138" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H138" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="139">
@@ -3752,10 +3752,10 @@
         <v>37</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D139" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E139" s="1" t="n">
         <v>0</v>
@@ -3764,10 +3764,10 @@
         <v>410000</v>
       </c>
       <c r="G139" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H139" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="140">
@@ -3776,22 +3776,22 @@
         <v>38</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D140" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F140" s="7" t="n">
         <v>410000</v>
       </c>
       <c r="G140" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H140" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="141">
@@ -3800,10 +3800,10 @@
         <v>39</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D141" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E141" s="1" t="n">
         <v>0</v>
@@ -3812,10 +3812,10 @@
         <v>440000</v>
       </c>
       <c r="G141" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H141" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="142">
@@ -3824,7 +3824,7 @@
         <v>40</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D142" s="1" t="n">
         <v>0</v>
@@ -3836,10 +3836,10 @@
         <v>440000</v>
       </c>
       <c r="G142" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H142" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="143">
@@ -3848,22 +3848,22 @@
         <v>41</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D143" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F143" s="7" t="n">
         <v>440000</v>
       </c>
       <c r="G143" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H143" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="144">
@@ -3872,7 +3872,7 @@
         <v>42</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D144" s="1" t="n">
         <v>0</v>
@@ -3884,10 +3884,10 @@
         <v>650000</v>
       </c>
       <c r="G144" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H144" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="145">
@@ -3896,10 +3896,10 @@
         <v>43</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D145" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E145" s="1" t="n">
         <v>0</v>
@@ -3908,10 +3908,10 @@
         <v>650000</v>
       </c>
       <c r="G145" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H145" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="146">
@@ -3920,22 +3920,22 @@
         <v>44</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D146" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F146" s="7" t="n">
         <v>650000</v>
       </c>
       <c r="G146" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H146" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="147">
@@ -3944,10 +3944,10 @@
         <v>45</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D147" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E147" s="1" t="n">
         <v>0</v>
@@ -3956,10 +3956,10 @@
         <v>880000</v>
       </c>
       <c r="G147" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H147" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="148">
@@ -3968,7 +3968,7 @@
         <v>46</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D148" s="1" t="n">
         <v>0</v>
@@ -3980,10 +3980,10 @@
         <v>880000</v>
       </c>
       <c r="G148" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H148" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="149">
@@ -3992,22 +3992,22 @@
         <v>47</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D149" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F149" s="7" t="n">
         <v>880000</v>
       </c>
       <c r="G149" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H149" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="150">
@@ -4016,7 +4016,7 @@
         <v>48</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D150" s="1" t="n">
         <v>0</v>
@@ -4028,10 +4028,10 @@
         <v>1300000</v>
       </c>
       <c r="G150" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H150" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="151">
@@ -4040,10 +4040,10 @@
         <v>49</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D151" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E151" s="1" t="n">
         <v>0</v>
@@ -4052,10 +4052,10 @@
         <v>1300000</v>
       </c>
       <c r="G151" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H151" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="152">
@@ -4064,22 +4064,22 @@
         <v>50</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D152" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F152" s="7" t="n">
         <v>1300000</v>
       </c>
       <c r="G152" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H152" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="153">
@@ -4088,10 +4088,10 @@
         <v>51</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D153" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E153" s="1" t="n">
         <v>0</v>
@@ -4100,10 +4100,10 @@
         <v>1470000</v>
       </c>
       <c r="G153" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H153" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="154">
@@ -4112,7 +4112,7 @@
         <v>52</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D154" s="1" t="n">
         <v>0</v>
@@ -4124,10 +4124,10 @@
         <v>1470000</v>
       </c>
       <c r="G154" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H154" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="155">
@@ -4136,22 +4136,22 @@
         <v>53</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D155" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F155" s="7" t="n">
         <v>1470000</v>
       </c>
       <c r="G155" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H155" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="156">
@@ -4160,7 +4160,7 @@
         <v>54</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D156" s="1" t="n">
         <v>0</v>
@@ -4172,10 +4172,10 @@
         <v>2160000</v>
       </c>
       <c r="G156" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H156" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="157">
@@ -4184,10 +4184,10 @@
         <v>55</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D157" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E157" s="1" t="n">
         <v>0</v>
@@ -4196,10 +4196,10 @@
         <v>2160000</v>
       </c>
       <c r="G157" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H157" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="158">
@@ -4208,22 +4208,22 @@
         <v>56</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D158" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F158" s="7" t="n">
         <v>2160000</v>
       </c>
       <c r="G158" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H158" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="159">
@@ -4232,10 +4232,10 @@
         <v>57</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D159" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E159" s="1" t="n">
         <v>0</v>
@@ -4244,10 +4244,10 @@
         <v>2850000</v>
       </c>
       <c r="G159" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H159" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="160">
@@ -4256,7 +4256,7 @@
         <v>58</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D160" s="1" t="n">
         <v>0</v>
@@ -4268,10 +4268,10 @@
         <v>4850000</v>
       </c>
       <c r="G160" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H160" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="161">
@@ -4280,22 +4280,22 @@
         <v>59</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D161" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F161" s="7" t="n">
         <v>4850000</v>
       </c>
       <c r="G161" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H161" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="162">
@@ -4304,7 +4304,7 @@
         <v>60</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D162" s="1" t="n">
         <v>0</v>
@@ -4316,10 +4316,10 @@
         <v>5760000</v>
       </c>
       <c r="G162" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H162" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="163">
@@ -4328,10 +4328,10 @@
         <v>61</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D163" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E163" s="1" t="n">
         <v>0</v>
@@ -4340,10 +4340,10 @@
         <v>6760000</v>
       </c>
       <c r="G163" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H163" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="164">
@@ -4352,22 +4352,22 @@
         <v>62</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D164" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F164" s="7" t="n">
         <v>7760000</v>
       </c>
       <c r="G164" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H164" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="165">
@@ -4376,10 +4376,10 @@
         <v>63</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D165" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E165" s="1" t="n">
         <v>0</v>
@@ -4388,10 +4388,10 @@
         <v>8490000</v>
       </c>
       <c r="G165" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H165" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="166">
@@ -4400,7 +4400,7 @@
         <v>64</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D166" s="1" t="n">
         <v>0</v>
@@ -4412,10 +4412,10 @@
         <v>7490000</v>
       </c>
       <c r="G166" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H166" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="167">
@@ -4424,22 +4424,22 @@
         <v>65</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D167" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F167" s="7" t="n">
         <v>8490000</v>
       </c>
       <c r="G167" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H167" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="168">
@@ -4448,7 +4448,7 @@
         <v>66</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D168" s="1" t="n">
         <v>0</v>
@@ -4460,10 +4460,10 @@
         <v>9710000</v>
       </c>
       <c r="G168" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H168" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="169">
@@ -4472,10 +4472,10 @@
         <v>67</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D169" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E169" s="1" t="n">
         <v>0</v>
@@ -4484,10 +4484,10 @@
         <v>8800000</v>
       </c>
       <c r="G169" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H169" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="170">
@@ -4496,22 +4496,22 @@
         <v>68</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D170" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F170" s="7" t="n">
         <v>10000000</v>
       </c>
       <c r="G170" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H170" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="171">
@@ -4520,10 +4520,10 @@
         <v>69</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D171" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E171" s="1" t="n">
         <v>0</v>
@@ -4532,10 +4532,10 @@
         <v>23000000</v>
       </c>
       <c r="G171" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H171" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="172">
@@ -4544,7 +4544,7 @@
         <v>70</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D172" s="1" t="n">
         <v>0</v>
@@ -4556,10 +4556,10 @@
         <v>21000000</v>
       </c>
       <c r="G172" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H172" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="173">
@@ -4568,22 +4568,22 @@
         <v>71</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D173" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F173" s="7" t="n">
         <v>26000000</v>
       </c>
       <c r="G173" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H173" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="174">
@@ -4592,7 +4592,7 @@
         <v>72</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D174" s="1" t="n">
         <v>0</v>
@@ -4604,10 +4604,10 @@
         <v>30000000</v>
       </c>
       <c r="G174" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H174" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="175">
@@ -4616,10 +4616,10 @@
         <v>73</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D175" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E175" s="1" t="n">
         <v>0</v>
@@ -4628,10 +4628,10 @@
         <v>35000000</v>
       </c>
       <c r="G175" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H175" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="176">
@@ -4640,22 +4640,22 @@
         <v>74</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D176" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F176" s="7" t="n">
         <v>35000000</v>
       </c>
       <c r="G176" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H176" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="177">
@@ -4664,10 +4664,10 @@
         <v>75</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D177" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E177" s="1" t="n">
         <v>0</v>
@@ -4676,10 +4676,10 @@
         <v>50000000</v>
       </c>
       <c r="G177" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H177" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="178">
@@ -4688,7 +4688,7 @@
         <v>76</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D178" s="1" t="n">
         <v>0</v>
@@ -4700,10 +4700,10 @@
         <v>50000000</v>
       </c>
       <c r="G178" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H178" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="179">
@@ -4712,22 +4712,22 @@
         <v>77</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D179" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F179" s="7" t="n">
         <v>60000000</v>
       </c>
       <c r="G179" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H179" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="180">
@@ -4736,7 +4736,7 @@
         <v>78</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D180" s="1" t="n">
         <v>0</v>
@@ -4748,10 +4748,10 @@
         <v>65000000</v>
       </c>
       <c r="G180" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H180" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="181">
@@ -4760,10 +4760,10 @@
         <v>79</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D181" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E181" s="1" t="n">
         <v>0</v>
@@ -4772,10 +4772,10 @@
         <v>70000000</v>
       </c>
       <c r="G181" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H181" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="182">
@@ -4784,22 +4784,22 @@
         <v>80</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D182" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F182" s="7" t="n">
         <v>75000000</v>
       </c>
       <c r="G182" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H182" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="183">
@@ -4808,10 +4808,10 @@
         <v>81</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D183" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E183" s="1" t="n">
         <v>0</v>
@@ -4820,10 +4820,10 @@
         <v>80000000</v>
       </c>
       <c r="G183" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H183" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="184">
@@ -4832,7 +4832,7 @@
         <v>82</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D184" s="1" t="n">
         <v>0</v>
@@ -4844,10 +4844,10 @@
         <v>90000000</v>
       </c>
       <c r="G184" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H184" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="185">
@@ -4856,22 +4856,22 @@
         <v>83</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D185" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F185" s="7" t="n">
         <v>95000000</v>
       </c>
       <c r="G185" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H185" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="186">
@@ -4880,7 +4880,7 @@
         <v>84</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D186" s="1" t="n">
         <v>0</v>
@@ -4892,10 +4892,10 @@
         <v>100000000</v>
       </c>
       <c r="G186" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H186" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="187">
@@ -4904,10 +4904,10 @@
         <v>85</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D187" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E187" s="1" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         <v>105000000</v>
       </c>
       <c r="G187" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H187" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="188">
@@ -4928,22 +4928,22 @@
         <v>86</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D188" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F188" s="7" t="n">
         <v>110000000</v>
       </c>
       <c r="G188" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H188" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="189">
@@ -4952,10 +4952,10 @@
         <v>87</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D189" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E189" s="1" t="n">
         <v>0</v>
@@ -4964,10 +4964,10 @@
         <v>110000000</v>
       </c>
       <c r="G189" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H189" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="190">
@@ -4976,7 +4976,7 @@
         <v>88</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D190" s="1" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>120000000</v>
       </c>
       <c r="G190" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H190" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="191">
@@ -5000,22 +5000,22 @@
         <v>89</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D191" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F191" s="7" t="n">
         <v>120000000</v>
       </c>
       <c r="G191" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H191" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="192">
@@ -5024,7 +5024,7 @@
         <v>90</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D192" s="1" t="n">
         <v>0</v>
@@ -5036,10 +5036,10 @@
         <v>30000000</v>
       </c>
       <c r="G192" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H192" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="193">
@@ -5048,10 +5048,10 @@
         <v>91</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D193" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E193" s="1" t="n">
         <v>0</v>
@@ -5060,10 +5060,10 @@
         <v>130000000</v>
       </c>
       <c r="G193" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H193" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="194">
@@ -5072,22 +5072,22 @@
         <v>92</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D194" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F194" s="7" t="n">
         <v>150000000</v>
       </c>
       <c r="G194" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H194" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="195">
@@ -5096,10 +5096,10 @@
         <v>93</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D195" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E195" s="1" t="n">
         <v>0</v>
@@ -5108,10 +5108,10 @@
         <v>160000000</v>
       </c>
       <c r="G195" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H195" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="196">
@@ -5120,7 +5120,7 @@
         <v>94</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D196" s="1" t="n">
         <v>0</v>
@@ -5132,10 +5132,10 @@
         <v>160000000</v>
       </c>
       <c r="G196" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H196" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="197">
@@ -5144,22 +5144,22 @@
         <v>95</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D197" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F197" s="7" t="n">
         <v>170000000</v>
       </c>
       <c r="G197" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H197" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="198">
@@ -5168,7 +5168,7 @@
         <v>96</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D198" s="1" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>190000000</v>
       </c>
       <c r="G198" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H198" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="199">
@@ -5192,10 +5192,10 @@
         <v>97</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D199" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E199" s="1" t="n">
         <v>0</v>
@@ -5204,10 +5204,10 @@
         <v>200000000</v>
       </c>
       <c r="G199" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H199" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="200">
@@ -5216,22 +5216,22 @@
         <v>98</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D200" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F200" s="7" t="n">
         <v>200000000</v>
       </c>
       <c r="G200" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H200" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="201">
@@ -5240,10 +5240,10 @@
         <v>99</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D201" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E201" s="1" t="n">
         <v>0</v>
@@ -5252,10 +5252,10 @@
         <v>0</v>
       </c>
       <c r="G201" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H201" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="202">
@@ -5281,7 +5281,7 @@
         <v>0</v>
       </c>
       <c r="D203" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E203" s="1" t="n">
         <v>0</v>
@@ -5290,10 +5290,10 @@
         <v>900</v>
       </c>
       <c r="G203" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H203" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="204">
@@ -5305,7 +5305,7 @@
         <v>0</v>
       </c>
       <c r="D204" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E204" s="1" t="n">
         <v>0</v>
@@ -5314,10 +5314,10 @@
         <v>780</v>
       </c>
       <c r="G204" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H204" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="205">
@@ -5326,22 +5326,22 @@
         <v>7</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D205" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F205" s="7" t="n">
         <v>960</v>
       </c>
       <c r="G205" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H205" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="206">
@@ -5353,7 +5353,7 @@
         <v>0</v>
       </c>
       <c r="D206" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E206" s="1" t="n">
         <v>0</v>
@@ -5362,10 +5362,10 @@
         <v>1000</v>
       </c>
       <c r="G206" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H206" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="207">
@@ -5374,22 +5374,22 @@
         <v>9</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D207" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F207" s="7" t="n">
         <v>1920</v>
       </c>
       <c r="G207" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H207" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="208">
@@ -5401,7 +5401,7 @@
         <v>0</v>
       </c>
       <c r="D208" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E208" s="1" t="n">
         <v>0</v>
@@ -5410,10 +5410,10 @@
         <v>1920</v>
       </c>
       <c r="G208" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H208" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="209">
@@ -5425,7 +5425,7 @@
         <v>0</v>
       </c>
       <c r="D209" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E209" s="1" t="n">
         <v>0</v>
@@ -5434,10 +5434,10 @@
         <v>1920</v>
       </c>
       <c r="G209" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H209" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="210">
@@ -5446,22 +5446,22 @@
         <v>12</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D210" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F210" s="7" t="n">
         <v>3840</v>
       </c>
       <c r="G210" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H210" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="211">
@@ -5473,7 +5473,7 @@
         <v>0</v>
       </c>
       <c r="D211" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E211" s="1" t="n">
         <v>0</v>
@@ -5482,10 +5482,10 @@
         <v>3840</v>
       </c>
       <c r="G211" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H211" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="212">
@@ -5494,22 +5494,22 @@
         <v>14</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D212" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F212" s="7" t="n">
         <v>3840</v>
       </c>
       <c r="G212" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H212" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="213">
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="D213" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E213" s="1" t="n">
         <v>0</v>
@@ -5530,10 +5530,10 @@
         <v>7680</v>
       </c>
       <c r="G213" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H213" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="214">
@@ -5545,7 +5545,7 @@
         <v>0</v>
       </c>
       <c r="D214" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E214" s="1" t="n">
         <v>0</v>
@@ -5554,10 +5554,10 @@
         <v>7680</v>
       </c>
       <c r="G214" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H214" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="215">
@@ -5566,22 +5566,22 @@
         <v>17</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D215" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F215" s="7" t="n">
         <v>7680</v>
       </c>
       <c r="G215" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H215" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="216">
@@ -5593,7 +5593,7 @@
         <v>0</v>
       </c>
       <c r="D216" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E216" s="1" t="n">
         <v>0</v>
@@ -5602,10 +5602,10 @@
         <v>15360</v>
       </c>
       <c r="G216" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H216" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="217">
@@ -5614,22 +5614,22 @@
         <v>19</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D217" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F217" s="7" t="n">
         <v>15360</v>
       </c>
       <c r="G217" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H217" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="218">
@@ -5641,7 +5641,7 @@
         <v>0</v>
       </c>
       <c r="D218" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E218" s="1" t="n">
         <v>0</v>
@@ -5650,10 +5650,10 @@
         <v>15360</v>
       </c>
       <c r="G218" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H218" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="219">
@@ -5665,7 +5665,7 @@
         <v>0</v>
       </c>
       <c r="D219" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E219" s="1" t="n">
         <v>0</v>
@@ -5674,10 +5674,10 @@
         <v>30720</v>
       </c>
       <c r="G219" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H219" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="220">
@@ -5686,22 +5686,22 @@
         <v>22</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D220" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F220" s="7" t="n">
         <v>30720</v>
       </c>
       <c r="G220" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H220" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="221">
@@ -5713,7 +5713,7 @@
         <v>0</v>
       </c>
       <c r="D221" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E221" s="1" t="n">
         <v>0</v>
@@ -5722,10 +5722,10 @@
         <v>30720</v>
       </c>
       <c r="G221" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H221" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="222">
@@ -5734,22 +5734,22 @@
         <v>24</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D222" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F222" s="7" t="n">
         <v>61440</v>
       </c>
       <c r="G222" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H222" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="223">
@@ -5761,7 +5761,7 @@
         <v>0</v>
       </c>
       <c r="D223" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E223" s="1" t="n">
         <v>0</v>
@@ -5770,10 +5770,10 @@
         <v>61440</v>
       </c>
       <c r="G223" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H223" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="224">
@@ -5785,7 +5785,7 @@
         <v>0</v>
       </c>
       <c r="D224" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E224" s="1" t="n">
         <v>0</v>
@@ -5794,10 +5794,10 @@
         <v>61440</v>
       </c>
       <c r="G224" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H224" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="225">
@@ -5806,22 +5806,22 @@
         <v>27</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D225" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F225" s="7" t="n">
         <v>122880</v>
       </c>
       <c r="G225" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H225" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="226">
@@ -5833,7 +5833,7 @@
         <v>0</v>
       </c>
       <c r="D226" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E226" s="1" t="n">
         <v>0</v>
@@ -5842,10 +5842,10 @@
         <v>122880</v>
       </c>
       <c r="G226" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H226" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="227">
@@ -5854,22 +5854,22 @@
         <v>29</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D227" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F227" s="7" t="n">
         <v>122880</v>
       </c>
       <c r="G227" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H227" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="228">
@@ -5881,7 +5881,7 @@
         <v>0</v>
       </c>
       <c r="D228" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E228" s="1" t="n">
         <v>0</v>
@@ -5890,10 +5890,10 @@
         <v>180000</v>
       </c>
       <c r="G228" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H228" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="229">
@@ -5905,7 +5905,7 @@
         <v>0</v>
       </c>
       <c r="D229" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E229" s="1" t="n">
         <v>0</v>
@@ -5914,10 +5914,10 @@
         <v>180000</v>
       </c>
       <c r="G229" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H229" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="230">
@@ -5926,22 +5926,22 @@
         <v>32</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D230" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F230" s="7" t="n">
         <v>180000</v>
       </c>
       <c r="G230" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H230" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="231">
@@ -5953,7 +5953,7 @@
         <v>0</v>
       </c>
       <c r="D231" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E231" s="1" t="n">
         <v>0</v>
@@ -5962,10 +5962,10 @@
         <v>250000</v>
       </c>
       <c r="G231" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H231" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="232">
@@ -5974,22 +5974,22 @@
         <v>34</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D232" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F232" s="7" t="n">
         <v>250000</v>
       </c>
       <c r="G232" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H232" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="233">
@@ -6001,7 +6001,7 @@
         <v>0</v>
       </c>
       <c r="D233" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E233" s="1" t="n">
         <v>0</v>
@@ -6010,10 +6010,10 @@
         <v>250000</v>
       </c>
       <c r="G233" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H233" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="234">
@@ -6025,7 +6025,7 @@
         <v>0</v>
       </c>
       <c r="D234" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E234" s="1" t="n">
         <v>0</v>
@@ -6034,10 +6034,10 @@
         <v>360000</v>
       </c>
       <c r="G234" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H234" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="235">
@@ -6046,22 +6046,22 @@
         <v>37</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D235" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F235" s="7" t="n">
         <v>360000</v>
       </c>
       <c r="G235" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H235" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="236">
@@ -6073,7 +6073,7 @@
         <v>0</v>
       </c>
       <c r="D236" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E236" s="1" t="n">
         <v>0</v>
@@ -6082,10 +6082,10 @@
         <v>360000</v>
       </c>
       <c r="G236" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H236" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="237">
@@ -6094,22 +6094,22 @@
         <v>39</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D237" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F237" s="7" t="n">
         <v>390000</v>
       </c>
       <c r="G237" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H237" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="238">
@@ -6121,7 +6121,7 @@
         <v>0</v>
       </c>
       <c r="D238" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E238" s="1" t="n">
         <v>0</v>
@@ -6130,10 +6130,10 @@
         <v>390000</v>
       </c>
       <c r="G238" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H238" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="239">
@@ -6145,7 +6145,7 @@
         <v>0</v>
       </c>
       <c r="D239" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E239" s="1" t="n">
         <v>0</v>
@@ -6154,10 +6154,10 @@
         <v>390000</v>
       </c>
       <c r="G239" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H239" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="240">
@@ -6166,22 +6166,22 @@
         <v>42</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D240" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F240" s="7" t="n">
         <v>580000</v>
       </c>
       <c r="G240" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H240" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="241">
@@ -6193,7 +6193,7 @@
         <v>0</v>
       </c>
       <c r="D241" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E241" s="1" t="n">
         <v>0</v>
@@ -6202,10 +6202,10 @@
         <v>580000</v>
       </c>
       <c r="G241" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H241" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="242">
@@ -6214,22 +6214,22 @@
         <v>44</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D242" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F242" s="7" t="n">
         <v>580000</v>
       </c>
       <c r="G242" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H242" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="243">
@@ -6241,7 +6241,7 @@
         <v>0</v>
       </c>
       <c r="D243" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E243" s="1" t="n">
         <v>0</v>
@@ -6250,10 +6250,10 @@
         <v>780000</v>
       </c>
       <c r="G243" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H243" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="244">
@@ -6265,7 +6265,7 @@
         <v>0</v>
       </c>
       <c r="D244" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E244" s="1" t="n">
         <v>0</v>
@@ -6274,10 +6274,10 @@
         <v>780000</v>
       </c>
       <c r="G244" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H244" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="245">
@@ -6286,22 +6286,22 @@
         <v>47</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D245" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F245" s="7" t="n">
         <v>780000</v>
       </c>
       <c r="G245" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H245" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="246">
@@ -6313,7 +6313,7 @@
         <v>0</v>
       </c>
       <c r="D246" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E246" s="1" t="n">
         <v>0</v>
@@ -6322,10 +6322,10 @@
         <v>1150000</v>
       </c>
       <c r="G246" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H246" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="247">
@@ -6334,22 +6334,22 @@
         <v>49</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D247" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F247" s="7" t="n">
         <v>1150000</v>
       </c>
       <c r="G247" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H247" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="248">
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="D248" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E248" s="1" t="n">
         <v>0</v>
@@ -6370,10 +6370,10 @@
         <v>1150000</v>
       </c>
       <c r="G248" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H248" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="249">
@@ -6385,7 +6385,7 @@
         <v>0</v>
       </c>
       <c r="D249" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E249" s="1" t="n">
         <v>0</v>
@@ -6394,10 +6394,10 @@
         <v>1310000</v>
       </c>
       <c r="G249" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H249" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="250">
@@ -6406,22 +6406,22 @@
         <v>52</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D250" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F250" s="7" t="n">
         <v>1310000</v>
       </c>
       <c r="G250" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H250" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="251">
@@ -6433,7 +6433,7 @@
         <v>0</v>
       </c>
       <c r="D251" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E251" s="1" t="n">
         <v>0</v>
@@ -6442,10 +6442,10 @@
         <v>1310000</v>
       </c>
       <c r="G251" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H251" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="252">
@@ -6454,22 +6454,22 @@
         <v>54</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D252" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F252" s="7" t="n">
         <v>1920000</v>
       </c>
       <c r="G252" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H252" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="253">
@@ -6481,7 +6481,7 @@
         <v>0</v>
       </c>
       <c r="D253" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E253" s="1" t="n">
         <v>0</v>
@@ -6490,10 +6490,10 @@
         <v>1920000</v>
       </c>
       <c r="G253" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H253" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="254">
@@ -6505,7 +6505,7 @@
         <v>0</v>
       </c>
       <c r="D254" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E254" s="1" t="n">
         <v>0</v>
@@ -6514,10 +6514,10 @@
         <v>1920000</v>
       </c>
       <c r="G254" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H254" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="255">
@@ -6526,22 +6526,22 @@
         <v>57</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D255" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F255" s="7" t="n">
         <v>4200000</v>
       </c>
       <c r="G255" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H255" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="256">
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="D256" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E256" s="1" t="n">
         <v>0</v>
@@ -6562,10 +6562,10 @@
         <v>4200000</v>
       </c>
       <c r="G256" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H256" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="257">
@@ -6574,22 +6574,22 @@
         <v>59</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D257" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F257" s="7" t="n">
         <v>4200000</v>
       </c>
       <c r="G257" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H257" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="258">
@@ -6601,7 +6601,7 @@
         <v>0</v>
       </c>
       <c r="D258" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E258" s="1" t="n">
         <v>0</v>
@@ -6610,10 +6610,10 @@
         <v>5120000</v>
       </c>
       <c r="G258" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H258" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="259">
@@ -6625,7 +6625,7 @@
         <v>0</v>
       </c>
       <c r="D259" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E259" s="1" t="n">
         <v>0</v>
@@ -6634,10 +6634,10 @@
         <v>5120000</v>
       </c>
       <c r="G259" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H259" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="260">
@@ -6646,22 +6646,22 @@
         <v>62</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D260" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F260" s="7" t="n">
         <v>5120000</v>
       </c>
       <c r="G260" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H260" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="261">
@@ -6673,7 +6673,7 @@
         <v>0</v>
       </c>
       <c r="D261" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E261" s="1" t="n">
         <v>0</v>
@@ -6682,10 +6682,10 @@
         <v>7980000</v>
       </c>
       <c r="G261" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H261" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="262">
@@ -6694,22 +6694,22 @@
         <v>64</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D262" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F262" s="7" t="n">
         <v>7980000</v>
       </c>
       <c r="G262" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H262" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="263">
@@ -6721,7 +6721,7 @@
         <v>0</v>
       </c>
       <c r="D263" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E263" s="1" t="n">
         <v>0</v>
@@ -6730,10 +6730,10 @@
         <v>7980000</v>
       </c>
       <c r="G263" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H263" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="264">
@@ -6745,7 +6745,7 @@
         <v>0</v>
       </c>
       <c r="D264" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E264" s="1" t="n">
         <v>0</v>
@@ -6754,10 +6754,10 @@
         <v>8660000</v>
       </c>
       <c r="G264" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H264" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="265">
@@ -6766,22 +6766,22 @@
         <v>67</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D265" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F265" s="7" t="n">
         <v>8660000</v>
       </c>
       <c r="G265" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H265" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="266">
@@ -6793,7 +6793,7 @@
         <v>0</v>
       </c>
       <c r="D266" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E266" s="1" t="n">
         <v>0</v>
@@ -6802,10 +6802,10 @@
         <v>8660000</v>
       </c>
       <c r="G266" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H266" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="267">
@@ -6814,22 +6814,22 @@
         <v>69</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D267" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F267" s="7" t="n">
         <v>1700000</v>
       </c>
       <c r="G267" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H267" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="268">
@@ -6841,7 +6841,7 @@
         <v>0</v>
       </c>
       <c r="D268" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E268" s="1" t="n">
         <v>0</v>
@@ -6850,10 +6850,10 @@
         <v>20000000</v>
       </c>
       <c r="G268" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H268" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="269">
@@ -6865,7 +6865,7 @@
         <v>0</v>
       </c>
       <c r="D269" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E269" s="1" t="n">
         <v>0</v>
@@ -6874,10 +6874,10 @@
         <v>10000000</v>
       </c>
       <c r="G269" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H269" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="270">
@@ -6886,22 +6886,22 @@
         <v>72</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D270" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F270" s="7" t="n">
         <v>10000000</v>
       </c>
       <c r="G270" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H270" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="271">
@@ -6913,7 +6913,7 @@
         <v>0</v>
       </c>
       <c r="D271" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E271" s="1" t="n">
         <v>0</v>
@@ -6922,10 +6922,10 @@
         <v>10000000</v>
       </c>
       <c r="G271" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H271" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="272">
@@ -6934,22 +6934,22 @@
         <v>74</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D272" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F272" s="7" t="n">
         <v>10000000</v>
       </c>
       <c r="G272" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H272" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="273">
@@ -6961,7 +6961,7 @@
         <v>0</v>
       </c>
       <c r="D273" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E273" s="1" t="n">
         <v>0</v>
@@ -6970,10 +6970,10 @@
         <v>20000000</v>
       </c>
       <c r="G273" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H273" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="274">
@@ -6985,7 +6985,7 @@
         <v>0</v>
       </c>
       <c r="D274" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E274" s="1" t="n">
         <v>0</v>
@@ -6994,10 +6994,10 @@
         <v>20000000</v>
       </c>
       <c r="G274" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H274" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="275">
@@ -7006,22 +7006,22 @@
         <v>77</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D275" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F275" s="7" t="n">
         <v>30000000</v>
       </c>
       <c r="G275" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H275" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="276">
@@ -7033,7 +7033,7 @@
         <v>0</v>
       </c>
       <c r="D276" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E276" s="1" t="n">
         <v>0</v>
@@ -7042,10 +7042,10 @@
         <v>20000000</v>
       </c>
       <c r="G276" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H276" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="277">
@@ -7054,22 +7054,22 @@
         <v>79</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D277" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F277" s="7" t="n">
         <v>30000000</v>
       </c>
       <c r="G277" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H277" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="278">
@@ -7081,7 +7081,7 @@
         <v>0</v>
       </c>
       <c r="D278" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E278" s="1" t="n">
         <v>0</v>
@@ -7090,10 +7090,10 @@
         <v>30000000</v>
       </c>
       <c r="G278" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H278" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="279">
@@ -7105,7 +7105,7 @@
         <v>0</v>
       </c>
       <c r="D279" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E279" s="1" t="n">
         <v>0</v>
@@ -7114,10 +7114,10 @@
         <v>40000000</v>
       </c>
       <c r="G279" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H279" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="280">
@@ -7126,22 +7126,22 @@
         <v>82</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D280" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F280" s="7" t="n">
         <v>40000000</v>
       </c>
       <c r="G280" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H280" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="281">
@@ -7153,7 +7153,7 @@
         <v>0</v>
       </c>
       <c r="D281" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E281" s="1" t="n">
         <v>0</v>
@@ -7162,10 +7162,10 @@
         <v>40000000</v>
       </c>
       <c r="G281" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H281" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="282">
@@ -7174,22 +7174,22 @@
         <v>84</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D282" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F282" s="7" t="n">
         <v>40000000</v>
       </c>
       <c r="G282" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H282" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="283">
@@ -7201,7 +7201,7 @@
         <v>0</v>
       </c>
       <c r="D283" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E283" s="1" t="n">
         <v>0</v>
@@ -7210,10 +7210,10 @@
         <v>50000000</v>
       </c>
       <c r="G283" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H283" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="284">
@@ -7225,7 +7225,7 @@
         <v>0</v>
       </c>
       <c r="D284" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E284" s="1" t="n">
         <v>0</v>
@@ -7234,10 +7234,10 @@
         <v>50000000</v>
       </c>
       <c r="G284" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H284" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="285">
@@ -7246,22 +7246,22 @@
         <v>87</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D285" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F285" s="7" t="n">
         <v>60000000</v>
       </c>
       <c r="G285" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H285" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="286">
@@ -7273,7 +7273,7 @@
         <v>0</v>
       </c>
       <c r="D286" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E286" s="1" t="n">
         <v>0</v>
@@ -7282,10 +7282,10 @@
         <v>60000000</v>
       </c>
       <c r="G286" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H286" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="287">
@@ -7294,22 +7294,22 @@
         <v>89</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D287" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F287" s="7" t="n">
         <v>70000000</v>
       </c>
       <c r="G287" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H287" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="288">
@@ -7321,7 +7321,7 @@
         <v>0</v>
       </c>
       <c r="D288" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E288" s="1" t="n">
         <v>0</v>
@@ -7330,10 +7330,10 @@
         <v>80000000</v>
       </c>
       <c r="G288" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H288" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="289">
@@ -7345,7 +7345,7 @@
         <v>0</v>
       </c>
       <c r="D289" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E289" s="1" t="n">
         <v>0</v>
@@ -7354,10 +7354,10 @@
         <v>90000000</v>
       </c>
       <c r="G289" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H289" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="290">
@@ -7366,22 +7366,22 @@
         <v>92</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D290" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F290" s="7" t="n">
         <v>100000000</v>
       </c>
       <c r="G290" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H290" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="291">
@@ -7393,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="D291" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E291" s="1" t="n">
         <v>0</v>
@@ -7402,10 +7402,10 @@
         <v>90000000</v>
       </c>
       <c r="G291" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H291" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="292">
@@ -7414,22 +7414,22 @@
         <v>94</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D292" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F292" s="7" t="n">
         <v>120000000</v>
       </c>
       <c r="G292" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H292" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="293">
@@ -7441,7 +7441,7 @@
         <v>0</v>
       </c>
       <c r="D293" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E293" s="1" t="n">
         <v>0</v>
@@ -7450,10 +7450,10 @@
         <v>130000000</v>
       </c>
       <c r="G293" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H293" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="294">
@@ -7465,7 +7465,7 @@
         <v>0</v>
       </c>
       <c r="D294" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E294" s="1" t="n">
         <v>0</v>
@@ -7474,10 +7474,10 @@
         <v>150000000</v>
       </c>
       <c r="G294" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H294" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="295">
@@ -7486,22 +7486,22 @@
         <v>97</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D295" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F295" s="7" t="n">
         <v>150000000</v>
       </c>
       <c r="G295" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H295" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="296">
@@ -7513,7 +7513,7 @@
         <v>0</v>
       </c>
       <c r="D296" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E296" s="1" t="n">
         <v>0</v>
@@ -7522,10 +7522,10 @@
         <v>300000000</v>
       </c>
       <c r="G296" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H296" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="297">
@@ -7534,22 +7534,22 @@
         <v>99</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D297" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F297" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G297" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H297" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="298">
@@ -7572,22 +7572,22 @@
         <v>5</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D299" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F299" s="7" t="n">
         <v>1040</v>
       </c>
       <c r="G299" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H299" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="300">
@@ -7596,7 +7596,7 @@
         <v>6</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D300" s="1" t="n">
         <v>0</v>
@@ -7608,10 +7608,10 @@
         <v>1040</v>
       </c>
       <c r="G300" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H300" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="301">
@@ -7620,22 +7620,22 @@
         <v>7</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D301" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F301" s="7" t="n">
         <v>1040</v>
       </c>
       <c r="G301" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H301" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="302">
@@ -7644,7 +7644,7 @@
         <v>8</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D302" s="1" t="n">
         <v>0</v>
@@ -7656,10 +7656,10 @@
         <v>1800</v>
       </c>
       <c r="G302" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H302" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="303">
@@ -7668,7 +7668,7 @@
         <v>9</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D303" s="1" t="n">
         <v>0</v>
@@ -7680,10 +7680,10 @@
         <v>1800</v>
       </c>
       <c r="G303" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H303" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="304">
@@ -7692,22 +7692,22 @@
         <v>10</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D304" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F304" s="7" t="n">
         <v>1800</v>
       </c>
       <c r="G304" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H304" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="305">
@@ -7716,7 +7716,7 @@
         <v>11</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D305" s="1" t="n">
         <v>0</v>
@@ -7728,10 +7728,10 @@
         <v>1820</v>
       </c>
       <c r="G305" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H305" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="306">
@@ -7740,7 +7740,7 @@
         <v>12</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D306" s="1" t="n">
         <v>0</v>
@@ -7752,10 +7752,10 @@
         <v>4320</v>
       </c>
       <c r="G306" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H306" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="307">
@@ -7764,22 +7764,22 @@
         <v>13</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D307" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F307" s="7" t="n">
         <v>4320</v>
       </c>
       <c r="G307" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H307" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="308">
@@ -7788,7 +7788,7 @@
         <v>14</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D308" s="1" t="n">
         <v>0</v>
@@ -7800,10 +7800,10 @@
         <v>4320</v>
       </c>
       <c r="G308" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H308" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="309">
@@ -7812,22 +7812,22 @@
         <v>15</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D309" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F309" s="7" t="n">
         <v>8640</v>
       </c>
       <c r="G309" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H309" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="310">
@@ -7836,7 +7836,7 @@
         <v>16</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D310" s="1" t="n">
         <v>0</v>
@@ -7848,10 +7848,10 @@
         <v>8640</v>
       </c>
       <c r="G310" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H310" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="311">
@@ -7860,7 +7860,7 @@
         <v>17</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D311" s="1" t="n">
         <v>0</v>
@@ -7872,10 +7872,10 @@
         <v>8640</v>
       </c>
       <c r="G311" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H311" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="312">
@@ -7884,22 +7884,22 @@
         <v>18</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D312" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F312" s="7" t="n">
         <v>17280</v>
       </c>
       <c r="G312" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H312" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="313">
@@ -7908,7 +7908,7 @@
         <v>19</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D313" s="1" t="n">
         <v>0</v>
@@ -7920,10 +7920,10 @@
         <v>17280</v>
       </c>
       <c r="G313" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H313" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="314">
@@ -7932,7 +7932,7 @@
         <v>20</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D314" s="1" t="n">
         <v>0</v>
@@ -7944,10 +7944,10 @@
         <v>17280</v>
       </c>
       <c r="G314" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H314" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="315">
@@ -7956,22 +7956,22 @@
         <v>21</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D315" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F315" s="7" t="n">
         <v>34000</v>
       </c>
       <c r="G315" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H315" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="316">
@@ -7980,7 +7980,7 @@
         <v>22</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D316" s="1" t="n">
         <v>0</v>
@@ -7992,10 +7992,10 @@
         <v>34000</v>
       </c>
       <c r="G316" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H316" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="317">
@@ -8004,22 +8004,22 @@
         <v>23</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D317" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F317" s="7" t="n">
         <v>34000</v>
       </c>
       <c r="G317" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H317" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="318">
@@ -8028,7 +8028,7 @@
         <v>24</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D318" s="1" t="n">
         <v>0</v>
@@ -8040,10 +8040,10 @@
         <v>69000</v>
       </c>
       <c r="G318" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H318" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="319">
@@ -8052,7 +8052,7 @@
         <v>25</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D319" s="1" t="n">
         <v>0</v>
@@ -8064,10 +8064,10 @@
         <v>69000</v>
       </c>
       <c r="G319" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H319" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="320">
@@ -8076,22 +8076,22 @@
         <v>26</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D320" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F320" s="7" t="n">
         <v>69000</v>
       </c>
       <c r="G320" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H320" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="321">
@@ -8100,7 +8100,7 @@
         <v>27</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D321" s="1" t="n">
         <v>0</v>
@@ -8112,10 +8112,10 @@
         <v>140000</v>
       </c>
       <c r="G321" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H321" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="322">
@@ -8124,7 +8124,7 @@
         <v>28</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D322" s="1" t="n">
         <v>0</v>
@@ -8136,10 +8136,10 @@
         <v>140000</v>
       </c>
       <c r="G322" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H322" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="323">
@@ -8148,22 +8148,22 @@
         <v>29</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D323" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F323" s="7" t="n">
         <v>140000</v>
       </c>
       <c r="G323" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H323" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="324">
@@ -8172,7 +8172,7 @@
         <v>30</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D324" s="1" t="n">
         <v>0</v>
@@ -8184,10 +8184,10 @@
         <v>180000</v>
       </c>
       <c r="G324" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H324" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="325">
@@ -8196,22 +8196,22 @@
         <v>31</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D325" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F325" s="7" t="n">
         <v>180000</v>
       </c>
       <c r="G325" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H325" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="326">
@@ -8220,7 +8220,7 @@
         <v>32</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D326" s="1" t="n">
         <v>0</v>
@@ -8232,10 +8232,10 @@
         <v>180000</v>
       </c>
       <c r="G326" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H326" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="327">
@@ -8244,7 +8244,7 @@
         <v>33</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D327" s="1" t="n">
         <v>0</v>
@@ -8256,10 +8256,10 @@
         <v>290000</v>
       </c>
       <c r="G327" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H327" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="328">
@@ -8268,22 +8268,22 @@
         <v>34</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D328" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F328" s="7" t="n">
         <v>290000</v>
       </c>
       <c r="G328" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H328" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="329">
@@ -8292,7 +8292,7 @@
         <v>35</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D329" s="1" t="n">
         <v>0</v>
@@ -8304,10 +8304,10 @@
         <v>290000</v>
       </c>
       <c r="G329" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H329" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="330">
@@ -8316,7 +8316,7 @@
         <v>36</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D330" s="1" t="n">
         <v>0</v>
@@ -8328,10 +8328,10 @@
         <v>410000</v>
       </c>
       <c r="G330" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H330" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="331">
@@ -8340,22 +8340,22 @@
         <v>37</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D331" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F331" s="7" t="n">
         <v>410000</v>
       </c>
       <c r="G331" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H331" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="332">
@@ -8364,7 +8364,7 @@
         <v>38</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D332" s="1" t="n">
         <v>0</v>
@@ -8376,10 +8376,10 @@
         <v>410000</v>
       </c>
       <c r="G332" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H332" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="333">
@@ -8388,22 +8388,22 @@
         <v>39</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D333" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F333" s="7" t="n">
         <v>440000</v>
       </c>
       <c r="G333" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H333" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="334">
@@ -8412,7 +8412,7 @@
         <v>40</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D334" s="1" t="n">
         <v>0</v>
@@ -8424,10 +8424,10 @@
         <v>440000</v>
       </c>
       <c r="G334" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H334" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="335">
@@ -8436,7 +8436,7 @@
         <v>41</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D335" s="1" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>440000</v>
       </c>
       <c r="G335" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H335" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="336">
@@ -8460,22 +8460,22 @@
         <v>42</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D336" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F336" s="7" t="n">
         <v>640000</v>
       </c>
       <c r="G336" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H336" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="337">
@@ -8484,7 +8484,7 @@
         <v>43</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D337" s="1" t="n">
         <v>0</v>
@@ -8496,10 +8496,10 @@
         <v>640000</v>
       </c>
       <c r="G337" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H337" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="338">
@@ -8508,7 +8508,7 @@
         <v>44</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D338" s="1" t="n">
         <v>0</v>
@@ -8520,10 +8520,10 @@
         <v>640000</v>
       </c>
       <c r="G338" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H338" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="339">
@@ -8532,22 +8532,22 @@
         <v>45</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D339" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F339" s="7" t="n">
         <v>880000</v>
       </c>
       <c r="G339" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H339" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="340">
@@ -8556,7 +8556,7 @@
         <v>46</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D340" s="1" t="n">
         <v>0</v>
@@ -8568,10 +8568,10 @@
         <v>880000</v>
       </c>
       <c r="G340" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H340" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="341">
@@ -8580,22 +8580,22 @@
         <v>47</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D341" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F341" s="7" t="n">
         <v>880000</v>
       </c>
       <c r="G341" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H341" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="342">
@@ -8604,7 +8604,7 @@
         <v>48</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D342" s="1" t="n">
         <v>0</v>
@@ -8616,10 +8616,10 @@
         <v>1300000</v>
       </c>
       <c r="G342" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H342" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="343">
@@ -8628,7 +8628,7 @@
         <v>49</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D343" s="1" t="n">
         <v>0</v>
@@ -8640,10 +8640,10 @@
         <v>1300000</v>
       </c>
       <c r="G343" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H343" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="344">
@@ -8652,22 +8652,22 @@
         <v>50</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D344" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F344" s="7" t="n">
         <v>1300000</v>
       </c>
       <c r="G344" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H344" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="345">
@@ -8676,7 +8676,7 @@
         <v>51</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D345" s="1" t="n">
         <v>0</v>
@@ -8688,10 +8688,10 @@
         <v>1500000</v>
       </c>
       <c r="G345" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H345" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="346">
@@ -8700,7 +8700,7 @@
         <v>52</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D346" s="1" t="n">
         <v>0</v>
@@ -8712,10 +8712,10 @@
         <v>1500000</v>
       </c>
       <c r="G346" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H346" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="347">
@@ -8724,22 +8724,22 @@
         <v>53</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D347" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F347" s="7" t="n">
         <v>1500000</v>
       </c>
       <c r="G347" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H347" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="348">
@@ -8748,7 +8748,7 @@
         <v>54</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D348" s="1" t="n">
         <v>0</v>
@@ -8760,10 +8760,10 @@
         <v>2160000</v>
       </c>
       <c r="G348" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H348" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="349">
@@ -8772,22 +8772,22 @@
         <v>55</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D349" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F349" s="7" t="n">
         <v>2160000</v>
       </c>
       <c r="G349" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H349" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="350">
@@ -8796,7 +8796,7 @@
         <v>56</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D350" s="1" t="n">
         <v>0</v>
@@ -8808,10 +8808,10 @@
         <v>2160000</v>
       </c>
       <c r="G350" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H350" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="351">
@@ -8820,7 +8820,7 @@
         <v>57</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D351" s="1" t="n">
         <v>0</v>
@@ -8832,10 +8832,10 @@
         <v>3340000</v>
       </c>
       <c r="G351" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H351" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="352">
@@ -8844,22 +8844,22 @@
         <v>58</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D352" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F352" s="7" t="n">
         <v>4850000</v>
       </c>
       <c r="G352" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H352" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="353">
@@ -8868,7 +8868,7 @@
         <v>59</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D353" s="1" t="n">
         <v>0</v>
@@ -8880,10 +8880,10 @@
         <v>4350000</v>
       </c>
       <c r="G353" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H353" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="354">
@@ -8892,7 +8892,7 @@
         <v>60</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D354" s="1" t="n">
         <v>0</v>
@@ -8904,10 +8904,10 @@
         <v>6900000</v>
       </c>
       <c r="G354" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H354" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="355">
@@ -8916,22 +8916,22 @@
         <v>61</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D355" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F355" s="7" t="n">
         <v>6900000</v>
       </c>
       <c r="G355" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H355" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="356">
@@ -8940,7 +8940,7 @@
         <v>62</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D356" s="1" t="n">
         <v>0</v>
@@ -8952,10 +8952,10 @@
         <v>6900000</v>
       </c>
       <c r="G356" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H356" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="357">
@@ -8964,22 +8964,22 @@
         <v>63</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D357" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F357" s="7" t="n">
         <v>8000000</v>
       </c>
       <c r="G357" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H357" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="358">
@@ -8988,7 +8988,7 @@
         <v>64</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D358" s="1" t="n">
         <v>0</v>
@@ -9000,10 +9000,10 @@
         <v>8000000</v>
       </c>
       <c r="G358" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H358" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="359">
@@ -9012,7 +9012,7 @@
         <v>65</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D359" s="1" t="n">
         <v>0</v>
@@ -9024,10 +9024,10 @@
         <v>8000000</v>
       </c>
       <c r="G359" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H359" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="360">
@@ -9036,22 +9036,22 @@
         <v>66</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D360" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F360" s="7" t="n">
         <v>10000000</v>
       </c>
       <c r="G360" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H360" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="361">
@@ -9060,7 +9060,7 @@
         <v>67</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D361" s="1" t="n">
         <v>0</v>
@@ -9072,10 +9072,10 @@
         <v>9000000</v>
       </c>
       <c r="G361" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H361" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="362">
@@ -9084,7 +9084,7 @@
         <v>68</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D362" s="1" t="n">
         <v>0</v>
@@ -9096,10 +9096,10 @@
         <v>10000000</v>
       </c>
       <c r="G362" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H362" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="363">
@@ -9108,22 +9108,22 @@
         <v>69</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D363" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F363" s="7" t="n">
         <v>10000000</v>
       </c>
       <c r="G363" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H363" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="364">
@@ -9132,7 +9132,7 @@
         <v>70</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D364" s="1" t="n">
         <v>0</v>
@@ -9144,10 +9144,10 @@
         <v>10000000</v>
       </c>
       <c r="G364" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H364" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="365">
@@ -9156,22 +9156,22 @@
         <v>71</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D365" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F365" s="7" t="n">
         <v>20000000</v>
       </c>
       <c r="G365" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H365" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="366">
@@ -9180,7 +9180,7 @@
         <v>72</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D366" s="1" t="n">
         <v>0</v>
@@ -9192,10 +9192,10 @@
         <v>20000000</v>
       </c>
       <c r="G366" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H366" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="367">
@@ -9204,7 +9204,7 @@
         <v>73</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D367" s="1" t="n">
         <v>0</v>
@@ -9216,10 +9216,10 @@
         <v>20000000</v>
       </c>
       <c r="G367" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H367" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="368">
@@ -9228,22 +9228,22 @@
         <v>74</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D368" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F368" s="7" t="n">
         <v>20000000</v>
       </c>
       <c r="G368" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H368" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="369">
@@ -9252,7 +9252,7 @@
         <v>75</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D369" s="1" t="n">
         <v>0</v>
@@ -9264,10 +9264,10 @@
         <v>30000000</v>
       </c>
       <c r="G369" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H369" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="370">
@@ -9276,7 +9276,7 @@
         <v>76</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D370" s="1" t="n">
         <v>0</v>
@@ -9288,10 +9288,10 @@
         <v>30000000</v>
       </c>
       <c r="G370" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H370" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="371">
@@ -9300,22 +9300,22 @@
         <v>77</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D371" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F371" s="7" t="n">
         <v>30000000</v>
       </c>
       <c r="G371" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H371" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="372">
@@ -9324,7 +9324,7 @@
         <v>78</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D372" s="1" t="n">
         <v>0</v>
@@ -9336,10 +9336,10 @@
         <v>40000000</v>
       </c>
       <c r="G372" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H372" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="373">
@@ -9348,22 +9348,22 @@
         <v>79</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D373" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F373" s="7" t="n">
         <v>40000000</v>
       </c>
       <c r="G373" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H373" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="374">
@@ -9372,7 +9372,7 @@
         <v>80</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D374" s="1" t="n">
         <v>0</v>
@@ -9384,10 +9384,10 @@
         <v>40000000</v>
       </c>
       <c r="G374" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H374" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="375">
@@ -9396,7 +9396,7 @@
         <v>81</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D375" s="1" t="n">
         <v>0</v>
@@ -9408,10 +9408,10 @@
         <v>50000000</v>
       </c>
       <c r="G375" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H375" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="376">
@@ -9420,22 +9420,22 @@
         <v>82</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D376" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F376" s="7" t="n">
         <v>50000000</v>
       </c>
       <c r="G376" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H376" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="377">
@@ -9444,7 +9444,7 @@
         <v>83</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D377" s="1" t="n">
         <v>0</v>
@@ -9456,10 +9456,10 @@
         <v>60000000</v>
       </c>
       <c r="G377" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H377" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="378">
@@ -9468,7 +9468,7 @@
         <v>84</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D378" s="1" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>60000000</v>
       </c>
       <c r="G378" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H378" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="379">
@@ -9492,22 +9492,22 @@
         <v>85</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D379" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F379" s="7" t="n">
         <v>70000000</v>
       </c>
       <c r="G379" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H379" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="380">
@@ -9516,7 +9516,7 @@
         <v>86</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D380" s="1" t="n">
         <v>0</v>
@@ -9528,10 +9528,10 @@
         <v>80000000</v>
       </c>
       <c r="G380" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H380" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="381">
@@ -9540,22 +9540,22 @@
         <v>87</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D381" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F381" s="7" t="n">
         <v>90000000</v>
       </c>
       <c r="G381" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H381" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="382">
@@ -9564,7 +9564,7 @@
         <v>88</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D382" s="1" t="n">
         <v>0</v>
@@ -9576,10 +9576,10 @@
         <v>100000000</v>
       </c>
       <c r="G382" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H382" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="383">
@@ -9588,7 +9588,7 @@
         <v>89</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D383" s="1" t="n">
         <v>0</v>
@@ -9600,10 +9600,10 @@
         <v>100000000</v>
       </c>
       <c r="G383" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H383" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="384">
@@ -9612,22 +9612,22 @@
         <v>90</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D384" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F384" s="7" t="n">
         <v>110000000</v>
       </c>
       <c r="G384" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H384" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="385">
@@ -9636,7 +9636,7 @@
         <v>91</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D385" s="1" t="n">
         <v>0</v>
@@ -9648,10 +9648,10 @@
         <v>200000000</v>
       </c>
       <c r="G385" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H385" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="386">
@@ -9660,7 +9660,7 @@
         <v>92</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D386" s="1" t="n">
         <v>0</v>
@@ -9672,10 +9672,10 @@
         <v>130000000</v>
       </c>
       <c r="G386" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H386" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="387">
@@ -9684,22 +9684,22 @@
         <v>93</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D387" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F387" s="7" t="n">
         <v>130000000</v>
       </c>
       <c r="G387" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H387" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="388">
@@ -9708,7 +9708,7 @@
         <v>94</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D388" s="1" t="n">
         <v>0</v>
@@ -9720,10 +9720,10 @@
         <v>140000000</v>
       </c>
       <c r="G388" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H388" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="389">
@@ -9732,22 +9732,22 @@
         <v>95</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D389" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F389" s="7" t="n">
         <v>40000000</v>
       </c>
       <c r="G389" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H389" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="390">
@@ -9756,7 +9756,7 @@
         <v>96</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D390" s="1" t="n">
         <v>0</v>
@@ -9768,10 +9768,10 @@
         <v>150000000</v>
       </c>
       <c r="G390" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H390" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="391">
@@ -9780,7 +9780,7 @@
         <v>97</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D391" s="1" t="n">
         <v>0</v>
@@ -9792,10 +9792,10 @@
         <v>150000000</v>
       </c>
       <c r="G391" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H391" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="392">
@@ -9804,22 +9804,22 @@
         <v>98</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D392" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F392" s="7" t="n">
         <v>170000000</v>
       </c>
       <c r="G392" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H392" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="393">
@@ -9828,7 +9828,7 @@
         <v>99</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D393" s="1" t="n">
         <v>0</v>
@@ -9840,10 +9840,10 @@
         <v>0</v>
       </c>
       <c r="G393" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H393" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/resources/table/class.xlsx
+++ b/resources/table/class.xlsx
@@ -831,10 +831,10 @@
         <v>7</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>1</v>
@@ -854,10 +854,10 @@
         <v>8</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>1</v>
@@ -877,10 +877,10 @@
         <v>9</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>1</v>
@@ -969,10 +969,10 @@
         <v>13</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>1</v>
@@ -992,10 +992,10 @@
         <v>14</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>1</v>
@@ -1015,10 +1015,10 @@
         <v>15</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>1</v>
@@ -1107,10 +1107,10 @@
         <v>19</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>1</v>
@@ -1130,10 +1130,10 @@
         <v>20</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>1</v>
@@ -1153,10 +1153,10 @@
         <v>21</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>1</v>
@@ -1245,10 +1245,10 @@
         <v>25</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>1</v>
@@ -1268,10 +1268,10 @@
         <v>26</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" s="7" t="n">
         <v>1</v>
@@ -1291,10 +1291,10 @@
         <v>27</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" s="7" t="n">
         <v>1</v>
@@ -1383,10 +1383,10 @@
         <v>31</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" s="7" t="n">
         <v>1</v>
@@ -1406,10 +1406,10 @@
         <v>32</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" s="7" t="n">
         <v>1</v>
@@ -1429,10 +1429,10 @@
         <v>33</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" s="7" t="n">
         <v>1</v>
@@ -1521,10 +1521,10 @@
         <v>37</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" s="7" t="n">
         <v>1</v>
@@ -1544,10 +1544,10 @@
         <v>38</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" s="7" t="n">
         <v>1</v>
@@ -1567,10 +1567,10 @@
         <v>39</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" s="7" t="n">
         <v>1</v>
@@ -1659,10 +1659,10 @@
         <v>43</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" s="7" t="n">
         <v>1</v>
@@ -1682,10 +1682,10 @@
         <v>44</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" s="7" t="n">
         <v>1</v>
@@ -1705,10 +1705,10 @@
         <v>45</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" s="7" t="n">
         <v>1</v>
@@ -1797,10 +1797,10 @@
         <v>49</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" s="7" t="n">
         <v>1</v>
@@ -1820,10 +1820,10 @@
         <v>50</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" s="7" t="n">
         <v>1</v>
@@ -1843,10 +1843,10 @@
         <v>51</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" s="7" t="n">
         <v>1</v>
@@ -1935,10 +1935,10 @@
         <v>55</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61" s="7" t="n">
         <v>1</v>
@@ -1958,10 +1958,10 @@
         <v>56</v>
       </c>
       <c r="C62" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62" s="7" t="n">
         <v>1</v>
@@ -1981,10 +1981,10 @@
         <v>57</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63" s="7" t="n">
         <v>1</v>
@@ -2073,10 +2073,10 @@
         <v>61</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67" s="7" t="n">
         <v>1</v>
@@ -2096,10 +2096,10 @@
         <v>62</v>
       </c>
       <c r="C68" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D68" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" s="7" t="n">
         <v>1</v>
@@ -2119,10 +2119,10 @@
         <v>63</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69" s="7" t="n">
         <v>1</v>
@@ -2211,10 +2211,10 @@
         <v>67</v>
       </c>
       <c r="C73" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73" s="7" t="n">
         <v>1</v>
@@ -2234,10 +2234,10 @@
         <v>68</v>
       </c>
       <c r="C74" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D74" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74" s="7" t="n">
         <v>1</v>
@@ -2257,10 +2257,10 @@
         <v>69</v>
       </c>
       <c r="C75" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75" s="7" t="n">
         <v>1</v>
@@ -2349,10 +2349,10 @@
         <v>73</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E79" s="7" t="n">
         <v>1</v>
@@ -2372,10 +2372,10 @@
         <v>74</v>
       </c>
       <c r="C80" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D80" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E80" s="7" t="n">
         <v>1</v>
@@ -2395,10 +2395,10 @@
         <v>75</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E81" s="7" t="n">
         <v>1</v>
@@ -2487,10 +2487,10 @@
         <v>79</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E85" s="7" t="n">
         <v>1</v>
@@ -2510,10 +2510,10 @@
         <v>80</v>
       </c>
       <c r="C86" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D86" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E86" s="7" t="n">
         <v>1</v>
@@ -2533,10 +2533,10 @@
         <v>81</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E87" s="7" t="n">
         <v>1</v>
@@ -2625,10 +2625,10 @@
         <v>85</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E91" s="7" t="n">
         <v>1</v>
@@ -2648,10 +2648,10 @@
         <v>86</v>
       </c>
       <c r="C92" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D92" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E92" s="7" t="n">
         <v>1</v>
@@ -2671,10 +2671,10 @@
         <v>87</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D93" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E93" s="7" t="n">
         <v>1</v>
@@ -2763,10 +2763,10 @@
         <v>91</v>
       </c>
       <c r="C97" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D97" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" s="7" t="n">
         <v>1</v>
@@ -2786,10 +2786,10 @@
         <v>92</v>
       </c>
       <c r="C98" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D98" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E98" s="7" t="n">
         <v>1</v>
@@ -2809,10 +2809,10 @@
         <v>93</v>
       </c>
       <c r="C99" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D99" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E99" s="7" t="n">
         <v>1</v>
@@ -2901,10 +2901,10 @@
         <v>97</v>
       </c>
       <c r="C103" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D103" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E103" s="7" t="n">
         <v>1</v>
@@ -2924,10 +2924,10 @@
         <v>98</v>
       </c>
       <c r="C104" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D104" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E104" s="7" t="n">
         <v>1</v>
@@ -2947,10 +2947,10 @@
         <v>99</v>
       </c>
       <c r="C105" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D105" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E105" s="7" t="n">
         <v>1</v>
@@ -3008,10 +3008,10 @@
         <v>6</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D108" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E108" s="1" t="n">
         <v>0</v>
@@ -3056,10 +3056,10 @@
         <v>8</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D110" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E110" s="1" t="n">
         <v>1</v>
@@ -3104,10 +3104,10 @@
         <v>10</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D112" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E112" s="1" t="n">
         <v>0</v>
@@ -3152,10 +3152,10 @@
         <v>12</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D114" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E114" s="1" t="n">
         <v>0</v>
@@ -3200,10 +3200,10 @@
         <v>14</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D116" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E116" s="1" t="n">
         <v>1</v>
@@ -3248,10 +3248,10 @@
         <v>16</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D118" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E118" s="1" t="n">
         <v>0</v>
@@ -3296,10 +3296,10 @@
         <v>18</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D120" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E120" s="1" t="n">
         <v>0</v>
@@ -3344,10 +3344,10 @@
         <v>20</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D122" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E122" s="1" t="n">
         <v>1</v>
@@ -3392,10 +3392,10 @@
         <v>22</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D124" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E124" s="1" t="n">
         <v>0</v>
@@ -3440,10 +3440,10 @@
         <v>24</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D126" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E126" s="1" t="n">
         <v>0</v>
@@ -3488,10 +3488,10 @@
         <v>26</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D128" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E128" s="1" t="n">
         <v>1</v>
@@ -3536,10 +3536,10 @@
         <v>28</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D130" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E130" s="1" t="n">
         <v>0</v>
@@ -3584,10 +3584,10 @@
         <v>30</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D132" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E132" s="1" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>32</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D134" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E134" s="1" t="n">
         <v>1</v>
@@ -3680,10 +3680,10 @@
         <v>34</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D136" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E136" s="1" t="n">
         <v>0</v>
@@ -3728,10 +3728,10 @@
         <v>36</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D138" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E138" s="1" t="n">
         <v>0</v>
@@ -3776,10 +3776,10 @@
         <v>38</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D140" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E140" s="1" t="n">
         <v>1</v>
@@ -3824,10 +3824,10 @@
         <v>40</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D142" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E142" s="1" t="n">
         <v>0</v>
@@ -3872,10 +3872,10 @@
         <v>42</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D144" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E144" s="1" t="n">
         <v>0</v>
@@ -3920,10 +3920,10 @@
         <v>44</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D146" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E146" s="1" t="n">
         <v>1</v>
@@ -3968,10 +3968,10 @@
         <v>46</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D148" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E148" s="1" t="n">
         <v>0</v>
@@ -4016,10 +4016,10 @@
         <v>48</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D150" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E150" s="1" t="n">
         <v>0</v>
@@ -4064,10 +4064,10 @@
         <v>50</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D152" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E152" s="1" t="n">
         <v>1</v>
@@ -4112,10 +4112,10 @@
         <v>52</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D154" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E154" s="1" t="n">
         <v>0</v>
@@ -4160,10 +4160,10 @@
         <v>54</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D156" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E156" s="1" t="n">
         <v>0</v>
@@ -4208,10 +4208,10 @@
         <v>56</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D158" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E158" s="1" t="n">
         <v>1</v>
@@ -4256,10 +4256,10 @@
         <v>58</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D160" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E160" s="1" t="n">
         <v>0</v>
@@ -4304,10 +4304,10 @@
         <v>60</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D162" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E162" s="1" t="n">
         <v>0</v>
@@ -4352,10 +4352,10 @@
         <v>62</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D164" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E164" s="1" t="n">
         <v>1</v>
@@ -4400,10 +4400,10 @@
         <v>64</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D166" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E166" s="1" t="n">
         <v>0</v>
@@ -4448,10 +4448,10 @@
         <v>66</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D168" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E168" s="1" t="n">
         <v>0</v>
@@ -4496,10 +4496,10 @@
         <v>68</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D170" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E170" s="1" t="n">
         <v>1</v>
@@ -4544,10 +4544,10 @@
         <v>70</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D172" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E172" s="1" t="n">
         <v>0</v>
@@ -4592,10 +4592,10 @@
         <v>72</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D174" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E174" s="1" t="n">
         <v>0</v>
@@ -4640,10 +4640,10 @@
         <v>74</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D176" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E176" s="1" t="n">
         <v>1</v>
@@ -4688,10 +4688,10 @@
         <v>76</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D178" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E178" s="1" t="n">
         <v>0</v>
@@ -4736,10 +4736,10 @@
         <v>78</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D180" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E180" s="1" t="n">
         <v>0</v>
@@ -4784,10 +4784,10 @@
         <v>80</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D182" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E182" s="1" t="n">
         <v>1</v>
@@ -4832,10 +4832,10 @@
         <v>82</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D184" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E184" s="1" t="n">
         <v>0</v>
@@ -4880,10 +4880,10 @@
         <v>84</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D186" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E186" s="1" t="n">
         <v>0</v>
@@ -4928,10 +4928,10 @@
         <v>86</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D188" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E188" s="1" t="n">
         <v>1</v>
@@ -4976,10 +4976,10 @@
         <v>88</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D190" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E190" s="1" t="n">
         <v>0</v>
@@ -5024,10 +5024,10 @@
         <v>90</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D192" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E192" s="1" t="n">
         <v>0</v>
@@ -5072,10 +5072,10 @@
         <v>92</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D194" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E194" s="1" t="n">
         <v>1</v>
@@ -5120,10 +5120,10 @@
         <v>94</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D196" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E196" s="1" t="n">
         <v>0</v>
@@ -5168,10 +5168,10 @@
         <v>96</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D198" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E198" s="1" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>98</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D200" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E200" s="1" t="n">
         <v>1</v>
@@ -5278,10 +5278,10 @@
         <v>5</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D203" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E203" s="1" t="n">
         <v>0</v>
@@ -5302,10 +5302,10 @@
         <v>6</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D204" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E204" s="1" t="n">
         <v>0</v>
@@ -5350,10 +5350,10 @@
         <v>8</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D206" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E206" s="1" t="n">
         <v>0</v>
@@ -5398,10 +5398,10 @@
         <v>10</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D208" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E208" s="1" t="n">
         <v>0</v>
@@ -5422,10 +5422,10 @@
         <v>11</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D209" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E209" s="1" t="n">
         <v>0</v>
@@ -5470,10 +5470,10 @@
         <v>13</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D211" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E211" s="1" t="n">
         <v>0</v>
@@ -5518,10 +5518,10 @@
         <v>15</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D213" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E213" s="1" t="n">
         <v>0</v>
@@ -5542,10 +5542,10 @@
         <v>16</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D214" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E214" s="1" t="n">
         <v>0</v>
@@ -5590,10 +5590,10 @@
         <v>18</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D216" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E216" s="1" t="n">
         <v>0</v>
@@ -5638,10 +5638,10 @@
         <v>20</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D218" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E218" s="1" t="n">
         <v>0</v>
@@ -5662,10 +5662,10 @@
         <v>21</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D219" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E219" s="1" t="n">
         <v>0</v>
@@ -5710,10 +5710,10 @@
         <v>23</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D221" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E221" s="1" t="n">
         <v>0</v>
@@ -5758,10 +5758,10 @@
         <v>25</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D223" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E223" s="1" t="n">
         <v>0</v>
@@ -5782,10 +5782,10 @@
         <v>26</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D224" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E224" s="1" t="n">
         <v>0</v>
@@ -5830,10 +5830,10 @@
         <v>28</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D226" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E226" s="1" t="n">
         <v>0</v>
@@ -5878,10 +5878,10 @@
         <v>30</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D228" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E228" s="1" t="n">
         <v>0</v>
@@ -5902,10 +5902,10 @@
         <v>31</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D229" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E229" s="1" t="n">
         <v>0</v>
@@ -5950,10 +5950,10 @@
         <v>33</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D231" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E231" s="1" t="n">
         <v>0</v>
@@ -5998,10 +5998,10 @@
         <v>35</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D233" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E233" s="1" t="n">
         <v>0</v>
@@ -6022,10 +6022,10 @@
         <v>36</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D234" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E234" s="1" t="n">
         <v>0</v>
@@ -6070,10 +6070,10 @@
         <v>38</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D236" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E236" s="1" t="n">
         <v>0</v>
@@ -6118,10 +6118,10 @@
         <v>40</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D238" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E238" s="1" t="n">
         <v>0</v>
@@ -6142,10 +6142,10 @@
         <v>41</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D239" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E239" s="1" t="n">
         <v>0</v>
@@ -6190,10 +6190,10 @@
         <v>43</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D241" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E241" s="1" t="n">
         <v>0</v>
@@ -6238,10 +6238,10 @@
         <v>45</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D243" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E243" s="1" t="n">
         <v>0</v>
@@ -6262,10 +6262,10 @@
         <v>46</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D244" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E244" s="1" t="n">
         <v>0</v>
@@ -6310,10 +6310,10 @@
         <v>48</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D246" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E246" s="1" t="n">
         <v>0</v>
@@ -6358,10 +6358,10 @@
         <v>50</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D248" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E248" s="1" t="n">
         <v>0</v>
@@ -6382,10 +6382,10 @@
         <v>51</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D249" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E249" s="1" t="n">
         <v>0</v>
@@ -6430,10 +6430,10 @@
         <v>53</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D251" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E251" s="1" t="n">
         <v>0</v>
@@ -6478,10 +6478,10 @@
         <v>55</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D253" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E253" s="1" t="n">
         <v>0</v>
@@ -6502,10 +6502,10 @@
         <v>56</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D254" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E254" s="1" t="n">
         <v>0</v>
@@ -6550,10 +6550,10 @@
         <v>58</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D256" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E256" s="1" t="n">
         <v>0</v>
@@ -6598,10 +6598,10 @@
         <v>60</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D258" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E258" s="1" t="n">
         <v>0</v>
@@ -6622,10 +6622,10 @@
         <v>61</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D259" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E259" s="1" t="n">
         <v>0</v>
@@ -6670,10 +6670,10 @@
         <v>63</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D261" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E261" s="1" t="n">
         <v>0</v>
@@ -6718,10 +6718,10 @@
         <v>65</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D263" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E263" s="1" t="n">
         <v>0</v>
@@ -6742,10 +6742,10 @@
         <v>66</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D264" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E264" s="1" t="n">
         <v>0</v>
@@ -6790,10 +6790,10 @@
         <v>68</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D266" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E266" s="1" t="n">
         <v>0</v>
@@ -6838,10 +6838,10 @@
         <v>70</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D268" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E268" s="1" t="n">
         <v>0</v>
@@ -6862,10 +6862,10 @@
         <v>71</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D269" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E269" s="1" t="n">
         <v>0</v>
@@ -6910,10 +6910,10 @@
         <v>73</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D271" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E271" s="1" t="n">
         <v>0</v>
@@ -6958,10 +6958,10 @@
         <v>75</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D273" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E273" s="1" t="n">
         <v>0</v>
@@ -6982,10 +6982,10 @@
         <v>76</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D274" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E274" s="1" t="n">
         <v>0</v>
@@ -7030,10 +7030,10 @@
         <v>78</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D276" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E276" s="1" t="n">
         <v>0</v>
@@ -7078,10 +7078,10 @@
         <v>80</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D278" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E278" s="1" t="n">
         <v>0</v>
@@ -7102,10 +7102,10 @@
         <v>81</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D279" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E279" s="1" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>83</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D281" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E281" s="1" t="n">
         <v>0</v>
@@ -7198,10 +7198,10 @@
         <v>85</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D283" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E283" s="1" t="n">
         <v>0</v>
@@ -7222,10 +7222,10 @@
         <v>86</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D284" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E284" s="1" t="n">
         <v>0</v>
@@ -7270,10 +7270,10 @@
         <v>88</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D286" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E286" s="1" t="n">
         <v>0</v>
@@ -7318,10 +7318,10 @@
         <v>90</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D288" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E288" s="1" t="n">
         <v>0</v>
@@ -7342,10 +7342,10 @@
         <v>91</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D289" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E289" s="1" t="n">
         <v>0</v>
@@ -7390,10 +7390,10 @@
         <v>93</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D291" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E291" s="1" t="n">
         <v>0</v>
@@ -7438,10 +7438,10 @@
         <v>95</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D293" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E293" s="1" t="n">
         <v>0</v>
@@ -7462,10 +7462,10 @@
         <v>96</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D294" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E294" s="1" t="n">
         <v>0</v>
@@ -7510,10 +7510,10 @@
         <v>98</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D296" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E296" s="1" t="n">
         <v>0</v>
@@ -7596,10 +7596,10 @@
         <v>6</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D300" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E300" s="1" t="n">
         <v>0</v>
@@ -7644,10 +7644,10 @@
         <v>8</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D302" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E302" s="1" t="n">
         <v>0</v>
@@ -7668,10 +7668,10 @@
         <v>9</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D303" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E303" s="1" t="n">
         <v>0</v>
@@ -7716,10 +7716,10 @@
         <v>11</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D305" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E305" s="1" t="n">
         <v>0</v>
@@ -7740,10 +7740,10 @@
         <v>12</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D306" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E306" s="1" t="n">
         <v>0</v>
@@ -7788,10 +7788,10 @@
         <v>14</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D308" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E308" s="1" t="n">
         <v>0</v>
@@ -7836,10 +7836,10 @@
         <v>16</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D310" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E310" s="1" t="n">
         <v>0</v>
@@ -7860,10 +7860,10 @@
         <v>17</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D311" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E311" s="1" t="n">
         <v>0</v>
@@ -7908,10 +7908,10 @@
         <v>19</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D313" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E313" s="1" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>20</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D314" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E314" s="1" t="n">
         <v>0</v>
@@ -7980,10 +7980,10 @@
         <v>22</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D316" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E316" s="1" t="n">
         <v>0</v>
@@ -8028,10 +8028,10 @@
         <v>24</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D318" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E318" s="1" t="n">
         <v>0</v>
@@ -8052,10 +8052,10 @@
         <v>25</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D319" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E319" s="1" t="n">
         <v>0</v>
@@ -8100,10 +8100,10 @@
         <v>27</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D321" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E321" s="1" t="n">
         <v>0</v>
@@ -8124,10 +8124,10 @@
         <v>28</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D322" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E322" s="1" t="n">
         <v>0</v>
@@ -8172,10 +8172,10 @@
         <v>30</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D324" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E324" s="1" t="n">
         <v>0</v>
@@ -8220,10 +8220,10 @@
         <v>32</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D326" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E326" s="1" t="n">
         <v>0</v>
@@ -8244,10 +8244,10 @@
         <v>33</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D327" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E327" s="1" t="n">
         <v>0</v>
@@ -8292,10 +8292,10 @@
         <v>35</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D329" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E329" s="1" t="n">
         <v>0</v>
@@ -8316,10 +8316,10 @@
         <v>36</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D330" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E330" s="1" t="n">
         <v>0</v>
@@ -8364,10 +8364,10 @@
         <v>38</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D332" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E332" s="1" t="n">
         <v>0</v>
@@ -8412,10 +8412,10 @@
         <v>40</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D334" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E334" s="1" t="n">
         <v>0</v>
@@ -8436,10 +8436,10 @@
         <v>41</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D335" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E335" s="1" t="n">
         <v>0</v>
@@ -8484,10 +8484,10 @@
         <v>43</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D337" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E337" s="1" t="n">
         <v>0</v>
@@ -8508,10 +8508,10 @@
         <v>44</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D338" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E338" s="1" t="n">
         <v>0</v>
@@ -8556,10 +8556,10 @@
         <v>46</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D340" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E340" s="1" t="n">
         <v>0</v>
@@ -8604,10 +8604,10 @@
         <v>48</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D342" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E342" s="1" t="n">
         <v>0</v>
@@ -8628,10 +8628,10 @@
         <v>49</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D343" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E343" s="1" t="n">
         <v>0</v>
@@ -8676,10 +8676,10 @@
         <v>51</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D345" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E345" s="1" t="n">
         <v>0</v>
@@ -8700,10 +8700,10 @@
         <v>52</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D346" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E346" s="1" t="n">
         <v>0</v>
@@ -8748,10 +8748,10 @@
         <v>54</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D348" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E348" s="1" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>56</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D350" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E350" s="1" t="n">
         <v>0</v>
@@ -8820,10 +8820,10 @@
         <v>57</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D351" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E351" s="1" t="n">
         <v>0</v>
@@ -8868,10 +8868,10 @@
         <v>59</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D353" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E353" s="1" t="n">
         <v>0</v>
@@ -8892,10 +8892,10 @@
         <v>60</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D354" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E354" s="1" t="n">
         <v>0</v>
@@ -8940,10 +8940,10 @@
         <v>62</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D356" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E356" s="1" t="n">
         <v>0</v>
@@ -8988,10 +8988,10 @@
         <v>64</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D358" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E358" s="1" t="n">
         <v>0</v>
@@ -9012,10 +9012,10 @@
         <v>65</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D359" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E359" s="1" t="n">
         <v>0</v>
@@ -9060,10 +9060,10 @@
         <v>67</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D361" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E361" s="1" t="n">
         <v>0</v>
@@ -9084,10 +9084,10 @@
         <v>68</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D362" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E362" s="1" t="n">
         <v>0</v>
@@ -9132,10 +9132,10 @@
         <v>70</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D364" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E364" s="1" t="n">
         <v>0</v>
@@ -9180,10 +9180,10 @@
         <v>72</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D366" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E366" s="1" t="n">
         <v>0</v>
@@ -9204,10 +9204,10 @@
         <v>73</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D367" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E367" s="1" t="n">
         <v>0</v>
@@ -9252,10 +9252,10 @@
         <v>75</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D369" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E369" s="1" t="n">
         <v>0</v>
@@ -9276,10 +9276,10 @@
         <v>76</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D370" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E370" s="1" t="n">
         <v>0</v>
@@ -9324,10 +9324,10 @@
         <v>78</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D372" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E372" s="1" t="n">
         <v>0</v>
@@ -9372,10 +9372,10 @@
         <v>80</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D374" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E374" s="1" t="n">
         <v>0</v>
@@ -9396,10 +9396,10 @@
         <v>81</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D375" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E375" s="1" t="n">
         <v>0</v>
@@ -9444,10 +9444,10 @@
         <v>83</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D377" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E377" s="1" t="n">
         <v>0</v>
@@ -9468,10 +9468,10 @@
         <v>84</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D378" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E378" s="1" t="n">
         <v>0</v>
@@ -9516,10 +9516,10 @@
         <v>86</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D380" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E380" s="1" t="n">
         <v>0</v>
@@ -9564,10 +9564,10 @@
         <v>88</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D382" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E382" s="1" t="n">
         <v>0</v>
@@ -9588,10 +9588,10 @@
         <v>89</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D383" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E383" s="1" t="n">
         <v>0</v>
@@ -9636,10 +9636,10 @@
         <v>91</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D385" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E385" s="1" t="n">
         <v>0</v>
@@ -9660,10 +9660,10 @@
         <v>92</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D386" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E386" s="1" t="n">
         <v>0</v>
@@ -9708,10 +9708,10 @@
         <v>94</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D388" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E388" s="1" t="n">
         <v>0</v>
@@ -9756,10 +9756,10 @@
         <v>96</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D390" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E390" s="1" t="n">
         <v>0</v>
@@ -9780,10 +9780,10 @@
         <v>97</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D391" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E391" s="1" t="n">
         <v>0</v>
@@ -9828,10 +9828,10 @@
         <v>99</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D393" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E393" s="1" t="n">
         <v>0</v>
